--- a/salidas/empresas/META.xlsx
+++ b/salidas/empresas/META.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B3" t="n">
-        <v>30.80496215820312</v>
+        <v>30.80496025085449</v>
       </c>
       <c r="C3" t="n">
         <v>31.10000038146973</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B4" t="n">
-        <v>21.5040397644043</v>
+        <v>21.50404167175293</v>
       </c>
       <c r="C4" t="n">
         <v>21.70999908447266</v>
@@ -545,11 +557,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B5" t="n">
-        <v>17.88866424560547</v>
+        <v>17.8886661529541</v>
       </c>
       <c r="C5" t="n">
         <v>18.05999946594238</v>
@@ -570,11 +582,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B6" t="n">
-        <v>21.45451545715332</v>
+        <v>21.45451354980469</v>
       </c>
       <c r="C6" t="n">
         <v>21.65999984741211</v>
@@ -595,11 +607,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90973472595215</v>
+        <v>20.90973091125488</v>
       </c>
       <c r="C7" t="n">
         <v>21.11000061035156</v>
@@ -620,7 +632,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B8" t="n">
@@ -645,11 +657,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B9" t="n">
-        <v>26.36746406555176</v>
+        <v>26.36746215820312</v>
       </c>
       <c r="C9" t="n">
         <v>26.6200008392334</v>
@@ -670,11 +682,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B10" t="n">
-        <v>30.68609428405762</v>
+        <v>30.68609619140625</v>
       </c>
       <c r="C10" t="n">
         <v>30.97999954223633</v>
@@ -695,11 +707,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B11" t="n">
-        <v>26.99148750305176</v>
+        <v>26.99148178100586</v>
       </c>
       <c r="C11" t="n">
         <v>27.25</v>
@@ -720,11 +732,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B12" t="n">
-        <v>25.33732795715332</v>
+        <v>25.33732604980469</v>
       </c>
       <c r="C12" t="n">
         <v>25.57999992370605</v>
@@ -745,11 +757,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B13" t="n">
-        <v>27.50655555725098</v>
+        <v>27.50655364990234</v>
       </c>
       <c r="C13" t="n">
         <v>27.77000045776367</v>
@@ -770,11 +782,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B14" t="n">
-        <v>24.11899757385254</v>
+        <v>24.11899566650391</v>
       </c>
       <c r="C14" t="n">
         <v>24.35000038146973</v>
@@ -795,11 +807,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B15" t="n">
-        <v>24.64396667480469</v>
+        <v>24.64396476745605</v>
       </c>
       <c r="C15" t="n">
         <v>24.8799991607666</v>
@@ -820,11 +832,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B16" t="n">
-        <v>36.45088577270508</v>
+        <v>36.45088195800781</v>
       </c>
       <c r="C16" t="n">
         <v>36.79999923706055</v>
@@ -845,11 +857,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B17" t="n">
-        <v>40.89829635620117</v>
+        <v>40.89829254150391</v>
       </c>
       <c r="C17" t="n">
         <v>41.29000091552734</v>
@@ -870,7 +882,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B18" t="n">
@@ -895,11 +907,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B19" t="n">
-        <v>49.73366928100586</v>
+        <v>49.73366546630859</v>
       </c>
       <c r="C19" t="n">
         <v>50.20999908447266</v>
@@ -920,7 +932,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B20" t="n">
@@ -945,11 +957,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B21" t="n">
-        <v>54.13154983520508</v>
+        <v>54.13154602050781</v>
       </c>
       <c r="C21" t="n">
         <v>54.65000152587891</v>
@@ -970,11 +982,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B22" t="n">
-        <v>61.97641372680664</v>
+        <v>61.97640991210938</v>
       </c>
       <c r="C22" t="n">
         <v>62.56999969482422</v>
@@ -999,11 +1011,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B23" t="n">
-        <v>67.81052398681641</v>
+        <v>67.81053924560547</v>
       </c>
       <c r="C23" t="n">
         <v>68.45999908447266</v>
@@ -1028,11 +1040,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B24" t="n">
-        <v>59.66851425170898</v>
+        <v>59.66851043701172</v>
       </c>
       <c r="C24" t="n">
         <v>60.2400016784668</v>
@@ -1057,11 +1069,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B25" t="n">
-        <v>59.2128791809082</v>
+        <v>59.21287155151367</v>
       </c>
       <c r="C25" t="n">
         <v>59.77999877929688</v>
@@ -1086,11 +1098,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B26" t="n">
-        <v>62.69948577880859</v>
+        <v>62.69948196411133</v>
       </c>
       <c r="C26" t="n">
         <v>63.29999923706055</v>
@@ -1115,11 +1127,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B27" t="n">
-        <v>66.65161895751953</v>
+        <v>66.65162658691406</v>
       </c>
       <c r="C27" t="n">
         <v>67.29000091552734</v>
@@ -1144,11 +1156,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B28" t="n">
-        <v>71.96078491210938</v>
+        <v>71.96077728271484</v>
       </c>
       <c r="C28" t="n">
         <v>72.65000152587891</v>
@@ -1173,11 +1185,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B29" t="n">
-        <v>74.11017608642578</v>
+        <v>74.11020660400391</v>
       </c>
       <c r="C29" t="n">
         <v>74.81999969482422</v>
@@ -1202,7 +1214,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B30" t="n">
@@ -1231,11 +1243,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B31" t="n">
-        <v>74.27857208251953</v>
+        <v>74.27858734130859</v>
       </c>
       <c r="C31" t="n">
         <v>74.98999786376953</v>
@@ -1260,11 +1272,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B32" t="n">
-        <v>76.96287536621094</v>
+        <v>76.96288299560547</v>
       </c>
       <c r="C32" t="n">
         <v>77.69999694824219</v>
@@ -1289,7 +1301,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B33" t="n">
@@ -1318,11 +1330,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B34" t="n">
-        <v>75.18986511230469</v>
+        <v>75.18985748291016</v>
       </c>
       <c r="C34" t="n">
         <v>75.91000366210938</v>
@@ -1347,11 +1359,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B35" t="n">
-        <v>78.2208251953125</v>
+        <v>78.22081756591797</v>
       </c>
       <c r="C35" t="n">
         <v>78.97000122070312</v>
@@ -1376,11 +1388,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B36" t="n">
-        <v>81.44000244140625</v>
+        <v>81.43999481201172</v>
       </c>
       <c r="C36" t="n">
         <v>82.22000122070312</v>
@@ -1405,7 +1417,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B37" t="n">
@@ -1434,11 +1446,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B38" t="n">
-        <v>78.43874359130859</v>
+        <v>78.43873596191406</v>
       </c>
       <c r="C38" t="n">
         <v>79.19000244140625</v>
@@ -1463,11 +1475,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B39" t="n">
-        <v>84.95630645751953</v>
+        <v>84.95632171630859</v>
       </c>
       <c r="C39" t="n">
         <v>85.76999664306641</v>
@@ -1492,11 +1504,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B40" t="n">
-        <v>93.11814117431641</v>
+        <v>93.11815643310547</v>
       </c>
       <c r="C40" t="n">
         <v>94.01000213623047</v>
@@ -1521,7 +1533,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B41" t="n">
@@ -1550,7 +1562,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B42" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B43" t="n">
@@ -1608,11 +1620,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B44" t="n">
-        <v>103.2510986328125</v>
+        <v>103.2510833740234</v>
       </c>
       <c r="C44" t="n">
         <v>104.2399978637695</v>
@@ -1637,7 +1649,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B45" t="n">
@@ -1666,11 +1678,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B46" t="n">
-        <v>111.1455001831055</v>
+        <v>111.1454772949219</v>
       </c>
       <c r="C46" t="n">
         <v>112.2099990844727</v>
@@ -1695,11 +1707,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B47" t="n">
-        <v>105.9056777954102</v>
+        <v>105.9056701660156</v>
       </c>
       <c r="C47" t="n">
         <v>106.9199981689453</v>
@@ -1724,7 +1736,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B48" t="n">
@@ -1753,11 +1765,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B49" t="n">
-        <v>116.4645385742188</v>
+        <v>116.4645233154297</v>
       </c>
       <c r="C49" t="n">
         <v>117.5800018310547</v>
@@ -1782,11 +1794,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B50" t="n">
-        <v>117.682861328125</v>
+        <v>117.6828689575195</v>
       </c>
       <c r="C50" t="n">
         <v>118.8099975585938</v>
@@ -1811,11 +1823,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B51" t="n">
-        <v>113.1958389282227</v>
+        <v>113.1958312988281</v>
       </c>
       <c r="C51" t="n">
         <v>114.2799987792969</v>
@@ -1840,7 +1852,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B52" t="n">
@@ -1869,11 +1881,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B53" t="n">
-        <v>124.9235229492188</v>
+        <v>124.9235305786133</v>
       </c>
       <c r="C53" t="n">
         <v>126.120002746582</v>
@@ -1898,7 +1910,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B54" t="n">
@@ -1927,11 +1939,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B55" t="n">
-        <v>129.747314453125</v>
+        <v>129.7473297119141</v>
       </c>
       <c r="C55" t="n">
         <v>130.9900054931641</v>
@@ -1956,11 +1968,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B56" t="n">
-        <v>117.2965698242188</v>
+        <v>117.2965621948242</v>
       </c>
       <c r="C56" t="n">
         <v>118.4199981689453</v>
@@ -1985,11 +1997,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B57" t="n">
-        <v>113.9585494995117</v>
+        <v>113.9585418701172</v>
       </c>
       <c r="C57" t="n">
         <v>115.0500030517578</v>
@@ -2014,7 +2026,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B58" t="n">
@@ -2043,7 +2055,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B59" t="n">
@@ -2072,11 +2084,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B60" t="n">
-        <v>140.7024078369141</v>
+        <v>140.7023620605469</v>
       </c>
       <c r="C60" t="n">
         <v>142.0500030517578</v>
@@ -2101,7 +2113,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B61" t="n">
@@ -2130,11 +2142,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B62" t="n">
-        <v>150.0231170654297</v>
+        <v>150.0231018066406</v>
       </c>
       <c r="C62" t="n">
         <v>151.4600067138672</v>
@@ -2159,11 +2171,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B63" t="n">
-        <v>149.5476531982422</v>
+        <v>149.5476837158203</v>
       </c>
       <c r="C63" t="n">
         <v>150.9799957275391</v>
@@ -2188,7 +2200,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B64" t="n">
@@ -2217,7 +2229,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B65" t="n">
@@ -2246,11 +2258,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B66" t="n">
-        <v>169.2489929199219</v>
+        <v>169.2489776611328</v>
       </c>
       <c r="C66" t="n">
         <v>170.8699951171875</v>
@@ -2275,11 +2287,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B67" t="n">
-        <v>178.3518218994141</v>
+        <v>178.3517761230469</v>
       </c>
       <c r="C67" t="n">
         <v>180.0599975585938</v>
@@ -2304,11 +2316,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B68" t="n">
-        <v>175.4991302490234</v>
+        <v>175.4991455078125</v>
       </c>
       <c r="C68" t="n">
         <v>177.1799926757812</v>
@@ -2333,7 +2345,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B69" t="n">
@@ -2362,11 +2374,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B70" t="n">
-        <v>185.1170043945312</v>
+        <v>185.1170196533203</v>
       </c>
       <c r="C70" t="n">
         <v>186.8899993896484</v>
@@ -2391,11 +2403,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B71" t="n">
-        <v>176.6283264160156</v>
+        <v>176.6283111572266</v>
       </c>
       <c r="C71" t="n">
         <v>178.3200073242188</v>
@@ -2420,7 +2432,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B72" t="n">
@@ -2449,11 +2461,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B73" t="n">
-        <v>170.3682708740234</v>
+        <v>170.3682556152344</v>
       </c>
       <c r="C73" t="n">
         <v>172</v>
@@ -2478,11 +2490,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B74" t="n">
-        <v>189.9606323242188</v>
+        <v>189.9606018066406</v>
       </c>
       <c r="C74" t="n">
         <v>191.7799987792969</v>
@@ -2507,7 +2519,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B75" t="n">
@@ -2536,7 +2548,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B76" t="n">
@@ -2565,7 +2577,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B77" t="n">
@@ -2594,11 +2606,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B78" t="n">
-        <v>162.8998260498047</v>
+        <v>162.8997955322266</v>
       </c>
       <c r="C78" t="n">
         <v>164.4600067138672</v>
@@ -2623,11 +2635,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B79" t="n">
-        <v>150.3499908447266</v>
+        <v>150.3500061035156</v>
       </c>
       <c r="C79" t="n">
         <v>151.7899932861328</v>
@@ -2652,7 +2664,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B80" t="n">
@@ -2681,11 +2693,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B81" t="n">
-        <v>129.8463592529297</v>
+        <v>129.8463745117188</v>
       </c>
       <c r="C81" t="n">
         <v>131.0899963378906</v>
@@ -2710,11 +2722,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B82" t="n">
-        <v>165.1086273193359</v>
+        <v>165.108642578125</v>
       </c>
       <c r="C82" t="n">
         <v>166.6900024414062</v>
@@ -2739,7 +2751,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B83" t="n">
@@ -2768,11 +2780,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B84" t="n">
-        <v>165.1086273193359</v>
+        <v>165.108642578125</v>
       </c>
       <c r="C84" t="n">
         <v>166.6900024414062</v>
@@ -2797,11 +2809,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B85" t="n">
-        <v>191.5652770996094</v>
+        <v>191.5652313232422</v>
       </c>
       <c r="C85" t="n">
         <v>193.3999938964844</v>
@@ -2826,11 +2838,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B86" t="n">
-        <v>175.786376953125</v>
+        <v>175.7864074707031</v>
       </c>
       <c r="C86" t="n">
         <v>177.4700012207031</v>
@@ -2855,11 +2867,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B87" t="n">
-        <v>191.1690521240234</v>
+        <v>191.1690368652344</v>
       </c>
       <c r="C87" t="n">
         <v>193</v>
@@ -2884,11 +2896,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B88" t="n">
-        <v>192.3873901367188</v>
+        <v>192.3873748779297</v>
       </c>
       <c r="C88" t="n">
         <v>194.2299957275391</v>
@@ -2913,11 +2925,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B89" t="n">
-        <v>183.9085540771484</v>
+        <v>183.9085998535156</v>
       </c>
       <c r="C89" t="n">
         <v>185.6699981689453</v>
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B90" t="n">
@@ -2971,7 +2983,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B91" t="n">
@@ -3000,11 +3012,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B92" t="n">
-        <v>199.7270965576172</v>
+        <v>199.7270812988281</v>
       </c>
       <c r="C92" t="n">
         <v>201.6399993896484</v>
@@ -3029,11 +3041,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B93" t="n">
-        <v>203.3027954101562</v>
+        <v>203.3028411865234</v>
       </c>
       <c r="C93" t="n">
         <v>205.25</v>
@@ -3058,11 +3070,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B94" t="n">
-        <v>199.9945220947266</v>
+        <v>199.9944915771484</v>
       </c>
       <c r="C94" t="n">
         <v>201.9100036621094</v>
@@ -3087,11 +3099,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B95" t="n">
-        <v>190.6440887451172</v>
+        <v>190.6440734863281</v>
       </c>
       <c r="C95" t="n">
         <v>192.4700012207031</v>
@@ -3116,7 +3128,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B96" t="n">
@@ -3145,7 +3157,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B97" t="n">
@@ -3174,7 +3186,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B98" t="n">
@@ -3203,11 +3215,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B99" t="n">
-        <v>224.9158325195312</v>
+        <v>224.9158172607422</v>
       </c>
       <c r="C99" t="n">
         <v>227.0700073242188</v>
@@ -3232,11 +3244,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B100" t="n">
-        <v>251.2634887695312</v>
+        <v>251.2634582519531</v>
       </c>
       <c r="C100" t="n">
         <v>253.6699981689453</v>
@@ -3261,11 +3273,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B101" t="n">
-        <v>290.41845703125</v>
+        <v>290.4185180664062</v>
       </c>
       <c r="C101" t="n">
         <v>293.2000122070312</v>
@@ -3290,11 +3302,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B102" t="n">
-        <v>259.4154052734375</v>
+        <v>259.4154357910156</v>
       </c>
       <c r="C102" t="n">
         <v>261.8999938964844</v>
@@ -3319,11 +3331,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B103" t="n">
-        <v>260.6138610839844</v>
+        <v>260.6139221191406</v>
       </c>
       <c r="C103" t="n">
         <v>263.1099853515625</v>
@@ -3348,11 +3360,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B104" t="n">
-        <v>274.3424377441406</v>
+        <v>274.3423767089844</v>
       </c>
       <c r="C104" t="n">
         <v>276.9700012207031</v>
@@ -3377,11 +3389,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B105" t="n">
-        <v>270.5685424804688</v>
+        <v>270.5685729980469</v>
       </c>
       <c r="C105" t="n">
         <v>273.1600036621094</v>
@@ -3406,11 +3418,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B106" t="n">
-        <v>255.8792419433594</v>
+        <v>255.8792572021484</v>
       </c>
       <c r="C106" t="n">
         <v>258.3299865722656</v>
@@ -3435,11 +3447,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B107" t="n">
-        <v>255.1759338378906</v>
+        <v>255.176025390625</v>
       </c>
       <c r="C107" t="n">
         <v>257.6199951171875</v>
@@ -3464,7 +3476,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B108" t="n">
@@ -3493,7 +3505,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B109" t="n">
@@ -3522,11 +3534,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B110" t="n">
-        <v>325.6113891601562</v>
+        <v>325.6114501953125</v>
       </c>
       <c r="C110" t="n">
         <v>328.7300109863281</v>
@@ -3551,11 +3563,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B111" t="n">
-        <v>344.4113464355469</v>
+        <v>344.411376953125</v>
       </c>
       <c r="C111" t="n">
         <v>347.7099914550781</v>
@@ -3580,7 +3592,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B112" t="n">
@@ -3609,7 +3621,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B113" t="n">
@@ -3638,11 +3650,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B114" t="n">
-        <v>336.1703186035156</v>
+        <v>336.1702880859375</v>
       </c>
       <c r="C114" t="n">
         <v>339.3900146484375</v>
@@ -3667,11 +3679,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B115" t="n">
-        <v>320.5003356933594</v>
+        <v>320.5003051757812</v>
       </c>
       <c r="C115" t="n">
         <v>323.5700073242188</v>
@@ -3696,11 +3708,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B116" t="n">
-        <v>321.3818664550781</v>
+        <v>321.3819274902344</v>
       </c>
       <c r="C116" t="n">
         <v>324.4599914550781</v>
@@ -3725,11 +3737,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B117" t="n">
-        <v>333.1591796875</v>
+        <v>333.1591491699219</v>
       </c>
       <c r="C117" t="n">
         <v>336.3500061035156</v>
@@ -3754,11 +3766,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B118" t="n">
-        <v>310.2882080078125</v>
+        <v>310.2882385253906</v>
       </c>
       <c r="C118" t="n">
         <v>313.260009765625</v>
@@ -3783,11 +3795,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B119" t="n">
-        <v>209.0279846191406</v>
+        <v>209.0279693603516</v>
       </c>
       <c r="C119" t="n">
         <v>211.0299987792969</v>
@@ -3812,7 +3824,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B120" t="n">
@@ -3841,11 +3853,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B121" t="n">
-        <v>198.5681610107422</v>
+        <v>198.5681762695312</v>
       </c>
       <c r="C121" t="n">
         <v>200.4700012207031</v>
@@ -3870,11 +3882,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B122" t="n">
-        <v>191.802978515625</v>
+        <v>191.8029632568359</v>
       </c>
       <c r="C122" t="n">
         <v>193.6399993896484</v>
@@ -3899,7 +3911,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B123" t="n">
@@ -3928,11 +3940,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B124" t="n">
-        <v>157.5906829833984</v>
+        <v>157.5906219482422</v>
       </c>
       <c r="C124" t="n">
         <v>159.1000061035156</v>
@@ -3957,11 +3969,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B125" t="n">
-        <v>161.3842926025391</v>
+        <v>161.3843078613281</v>
       </c>
       <c r="C125" t="n">
         <v>162.9299926757812</v>
@@ -3986,7 +3998,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B126" t="n">
@@ -4015,11 +4027,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B127" t="n">
-        <v>92.27620697021484</v>
+        <v>92.27621459960938</v>
       </c>
       <c r="C127" t="n">
         <v>93.16000366210938</v>
@@ -4044,11 +4056,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B128" t="n">
-        <v>116.979606628418</v>
+        <v>116.9795989990234</v>
       </c>
       <c r="C128" t="n">
         <v>118.0999984741211</v>
@@ -4073,11 +4085,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B129" t="n">
-        <v>119.1983489990234</v>
+        <v>119.198356628418</v>
       </c>
       <c r="C129" t="n">
         <v>120.3399963378906</v>
@@ -4102,11 +4114,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B130" t="n">
-        <v>147.5567626953125</v>
+        <v>147.5567321777344</v>
       </c>
       <c r="C130" t="n">
         <v>148.9700012207031</v>
@@ -4131,11 +4143,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B131" t="n">
-        <v>173.2803802490234</v>
+        <v>173.2803649902344</v>
       </c>
       <c r="C131" t="n">
         <v>174.9400024414062</v>
@@ -4160,7 +4172,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B132" t="n">
@@ -4189,11 +4201,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B133" t="n">
-        <v>238.0401458740234</v>
+        <v>238.0401306152344</v>
       </c>
       <c r="C133" t="n">
         <v>240.3200073242188</v>
@@ -4218,11 +4230,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B134" t="n">
-        <v>262.2086791992188</v>
+        <v>262.2086486816406</v>
       </c>
       <c r="C134" t="n">
         <v>264.7200012207031</v>
@@ -4247,11 +4259,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B135" t="n">
-        <v>284.2575073242188</v>
+        <v>284.2574768066406</v>
       </c>
       <c r="C135" t="n">
         <v>286.9800109863281</v>
@@ -4276,11 +4288,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B136" t="n">
-        <v>315.5775146484375</v>
+        <v>315.5774841308594</v>
       </c>
       <c r="C136" t="n">
         <v>318.6000061035156</v>
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B137" t="n">
@@ -4334,7 +4346,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B138" t="n">
@@ -4363,11 +4375,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B139" t="n">
-        <v>298.411865234375</v>
+        <v>298.4118957519531</v>
       </c>
       <c r="C139" t="n">
         <v>301.2699890136719</v>
@@ -4392,7 +4404,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B140" t="n">
@@ -4421,11 +4433,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B141" t="n">
-        <v>350.60205078125</v>
+        <v>350.6020202636719</v>
       </c>
       <c r="C141" t="n">
         <v>353.9599914550781</v>
@@ -4450,11 +4462,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B142" t="n">
-        <v>386.4388427734375</v>
+        <v>386.4388122558594</v>
       </c>
       <c r="C142" t="n">
         <v>390.1400146484375</v>
@@ -4479,7 +4491,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B143" t="n">
@@ -4508,11 +4520,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B144" t="n">
-        <v>481.4837036132812</v>
+        <v>481.4837341308594</v>
       </c>
       <c r="C144" t="n">
         <v>485.5799865722656</v>
@@ -4537,11 +4549,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B145" t="n">
-        <v>426.5411376953125</v>
+        <v>426.5411682128906</v>
       </c>
       <c r="C145" t="n">
         <v>430.1700134277344</v>
@@ -4566,11 +4578,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B146" t="n">
-        <v>462.8918762207031</v>
+        <v>462.891845703125</v>
       </c>
       <c r="C146" t="n">
         <v>466.8299865722656</v>
@@ -4595,7 +4607,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B147" t="n">
@@ -4624,11 +4636,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B148" t="n">
-        <v>471.2918701171875</v>
+        <v>471.2918395996094</v>
       </c>
       <c r="C148" t="n">
         <v>474.8299865722656</v>
@@ -4653,11 +4665,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B149" t="n">
-        <v>517.425537109375</v>
+        <v>517.4256591796875</v>
       </c>
       <c r="C149" t="n">
         <v>521.3099975585938</v>
@@ -4682,11 +4694,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B150" t="n">
-        <v>568.716552734375</v>
+        <v>568.7166137695312</v>
       </c>
       <c r="C150" t="n">
         <v>572.4400024414062</v>
@@ -4711,11 +4723,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B151" t="n">
-        <v>563.88818359375</v>
+        <v>563.8880615234375</v>
       </c>
       <c r="C151" t="n">
         <v>567.5800170898438</v>
@@ -4740,11 +4752,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B152" t="n">
-        <v>570.5843505859375</v>
+        <v>570.5844116210938</v>
       </c>
       <c r="C152" t="n">
         <v>574.3200073242188</v>
@@ -4769,11 +4781,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B153" t="n">
-        <v>582.1707153320312</v>
+        <v>582.1707763671875</v>
       </c>
       <c r="C153" t="n">
         <v>585.510009765625</v>
@@ -4798,11 +4810,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B154" t="n">
-        <v>685.2494506835938</v>
+        <v>685.24951171875</v>
       </c>
       <c r="C154" t="n">
         <v>689.1799926757812</v>
@@ -4827,7 +4839,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B155" t="n">
@@ -4856,11 +4868,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B156" t="n">
-        <v>573.582763671875</v>
+        <v>573.5828247070312</v>
       </c>
       <c r="C156" t="n">
         <v>576.3599853515625</v>
@@ -4885,7 +4897,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B157" t="n">
@@ -4914,11 +4926,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B158" t="n">
-        <v>644.3701171875</v>
+        <v>644.3700561523438</v>
       </c>
       <c r="C158" t="n">
         <v>647.489990234375</v>
@@ -4943,7 +4955,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B159" t="n">
@@ -4972,7 +4984,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B160" t="n">
@@ -5001,7 +5013,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B161" t="n">
@@ -5030,11 +5042,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B162" t="n">
-        <v>731.8973999023438</v>
+        <v>731.8973388671875</v>
       </c>
       <c r="C162" t="n">
         <v>734.3800048828125</v>
@@ -5059,11 +5071,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B163" t="n">
-        <v>646.1581420898438</v>
+        <v>646.158203125</v>
       </c>
       <c r="C163" t="n">
         <v>648.3499755859375</v>
@@ -5088,7 +5100,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B164" t="n">
@@ -5117,11 +5129,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B165" t="n">
-        <v>658.3950805664062</v>
+        <v>658.39501953125</v>
       </c>
       <c r="C165" t="n">
         <v>660.0900268554688</v>
@@ -5146,11 +5158,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B166" t="n">
-        <v>714.66015625</v>
+        <v>714.6602172851562</v>
       </c>
       <c r="C166" t="n">
         <v>716.5</v>
@@ -5175,7 +5187,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B167" t="n">
@@ -5204,7 +5216,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B168" t="n">
@@ -5233,7 +5245,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B169" t="n">
@@ -5262,7 +5274,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B170" t="n">
@@ -5291,7 +5303,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B171" t="n">
@@ -5320,7 +5332,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B172" t="n">
@@ -5349,7 +5361,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B173" t="n">
@@ -5378,32 +5390,32 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B174" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="C174" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="D174" t="n">
-        <v>368086100</v>
+        <v>403313700</v>
       </c>
       <c r="E174" t="n">
         <v>26.54</v>
       </c>
       <c r="F174" t="n">
-        <v>28.03692447573239</v>
+        <v>29.29879528468232</v>
       </c>
       <c r="G174" t="n">
         <v>2543000000</v>
       </c>
       <c r="H174" t="n">
-        <v>1892246237915.039</v>
+        <v>1977411438293.457</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1447448289421943</v>
+        <v>0.1585976012583563</v>
       </c>
     </row>
   </sheetData>
@@ -5435,75 +5447,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5539,13 +5551,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5581,13 +5593,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5623,13 +5635,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5665,13 +5677,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5707,13 +5719,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5749,13 +5761,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5791,13 +5803,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5833,13 +5845,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5866,7 +5878,7 @@
       <c r="I10" t="n">
         <v>0.6</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="K10" t="n">
@@ -5879,13 +5891,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5912,7 +5924,7 @@
       <c r="I11" t="n">
         <v>0.76</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K11" t="n">
@@ -5925,13 +5937,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -5958,7 +5970,7 @@
       <c r="I12" t="n">
         <v>0.9299999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="K12" t="n">
@@ -5971,13 +5983,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6004,7 +6016,7 @@
       <c r="I13" t="n">
         <v>1.06</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K13" t="n">
@@ -6017,13 +6029,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42033</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6050,7 +6062,7 @@
       <c r="I14" t="n">
         <v>1.1</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42033</v>
       </c>
       <c r="K14" t="n">
@@ -6063,13 +6075,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6096,7 +6108,7 @@
       <c r="I15" t="n">
         <v>1.03</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K15" t="n">
@@ -6109,13 +6121,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6142,7 +6154,7 @@
       <c r="I16" t="n">
         <v>0.98</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="K16" t="n">
@@ -6155,13 +6167,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6188,7 +6200,7 @@
       <c r="I17" t="n">
         <v>0.99</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K17" t="n">
@@ -6201,13 +6213,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6234,7 +6246,7 @@
       <c r="I18" t="n">
         <v>1.29</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="K18" t="n">
@@ -6247,13 +6259,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6280,7 +6292,7 @@
       <c r="I19" t="n">
         <v>1.63</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K19" t="n">
@@ -6293,13 +6305,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6326,7 +6338,7 @@
       <c r="I20" t="n">
         <v>2.09</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K20" t="n">
@@ -6339,13 +6351,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6372,7 +6384,7 @@
       <c r="I21" t="n">
         <v>2.6</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K21" t="n">
@@ -6385,13 +6397,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6418,7 +6430,7 @@
       <c r="I22" t="n">
         <v>3.49</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="K22" t="n">
@@ -6431,13 +6443,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6464,7 +6476,7 @@
       <c r="I23" t="n">
         <v>4.010000000000001</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K23" t="n">
@@ -6477,13 +6489,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6510,7 +6522,7 @@
       <c r="I24" t="n">
         <v>4.620000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K24" t="n">
@@ -6523,13 +6535,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6556,7 +6568,7 @@
       <c r="I25" t="n">
         <v>5.390000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K25" t="n">
@@ -6569,13 +6581,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6602,7 +6614,7 @@
       <c r="I26" t="n">
         <v>5.39</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="K26" t="n">
@@ -6615,13 +6627,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6648,7 +6660,7 @@
       <c r="I27" t="n">
         <v>6.039999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K27" t="n">
@@ -6661,13 +6673,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6694,7 +6706,7 @@
       <c r="I28" t="n">
         <v>6.459999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K28" t="n">
@@ -6707,13 +6719,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6740,7 +6752,7 @@
       <c r="I29" t="n">
         <v>6.629999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K29" t="n">
@@ -6753,13 +6765,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6786,7 +6798,7 @@
       <c r="I30" t="n">
         <v>7.57</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="K30" t="n">
@@ -6799,13 +6811,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6832,7 +6844,7 @@
       <c r="I31" t="n">
         <v>6.730000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K31" t="n">
@@ -6845,13 +6857,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6878,7 +6890,7 @@
       <c r="I32" t="n">
         <v>5.900000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K32" t="n">
@@ -6891,13 +6903,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6924,7 +6936,7 @@
       <c r="I33" t="n">
         <v>6.260000000000001</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K33" t="n">
@@ -6937,13 +6949,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -6970,7 +6982,7 @@
       <c r="I34" t="n">
         <v>6.43</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="K34" t="n">
@@ -6983,13 +6995,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7016,7 +7028,7 @@
       <c r="I35" t="n">
         <v>7.290000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K35" t="n">
@@ -7029,13 +7041,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7062,7 +7074,7 @@
       <c r="I36" t="n">
         <v>8.18</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K36" t="n">
@@ -7075,13 +7087,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7108,7 +7120,7 @@
       <c r="I37" t="n">
         <v>8.77</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K37" t="n">
@@ -7121,13 +7133,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7154,7 +7166,7 @@
       <c r="I38" t="n">
         <v>10.09</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="K38" t="n">
@@ -7167,13 +7179,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7200,7 +7212,7 @@
       <c r="I39" t="n">
         <v>11.68</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K39" t="n">
@@ -7213,13 +7225,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7246,7 +7258,7 @@
       <c r="I40" t="n">
         <v>13.49</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K40" t="n">
@@ -7259,13 +7271,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7292,7 +7304,7 @@
       <c r="I41" t="n">
         <v>14</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K41" t="n">
@@ -7305,13 +7317,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7338,7 +7350,7 @@
       <c r="I42" t="n">
         <v>13.77</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="K42" t="n">
@@ -7351,13 +7363,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7384,7 +7396,7 @@
       <c r="I43" t="n">
         <v>13.19</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K43" t="n">
@@ -7397,13 +7409,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7430,7 +7442,7 @@
       <c r="I44" t="n">
         <v>12.04</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K44" t="n">
@@ -7443,13 +7455,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7476,7 +7488,7 @@
       <c r="I45" t="n">
         <v>10.46</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K45" t="n">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I46" t="n">
         <v>8.590000000000002</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="K46" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I47" t="n">
         <v>8.07</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K47" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I48" t="n">
         <v>8.590000000000002</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K48" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I49" t="n">
         <v>11.34</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K49" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I50" t="n">
         <v>14.87</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="K50" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I51" t="n">
         <v>17.38</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K51" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I52" t="n">
         <v>19.56</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K52" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I53" t="n">
         <v>21.2</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K53" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I54" t="n">
         <v>23.86</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="K54" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I55" t="n">
         <v>25.58</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K55" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I56" t="n">
         <v>27.56</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K56" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I57" t="n">
         <v>22.58</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K57" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I58" t="n">
         <v>23.49</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="K58" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I59" t="n">
         <v>27.5</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K59" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I60" t="n">
         <v>26.54</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K60" t="n">
@@ -8204,57 +8216,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="C2" t="n">
@@ -8288,10 +8300,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C3" t="n">
@@ -8325,10 +8337,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C4" t="n">
@@ -8362,10 +8374,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="C5" t="n">
@@ -8399,10 +8411,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="C6" t="n">
@@ -8436,10 +8448,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C7" t="n">
@@ -8473,10 +8485,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C8" t="n">
@@ -8510,10 +8522,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C9" t="n">
@@ -8547,10 +8559,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C10" t="n">
@@ -8584,10 +8596,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="C11" t="n">
@@ -8621,10 +8633,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C12" t="n">
@@ -8658,10 +8670,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="C13" t="n">
@@ -8695,10 +8707,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C14" t="n">
@@ -8732,10 +8744,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42033</v>
       </c>
       <c r="C15" t="n">
@@ -8769,10 +8781,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C16" t="n">
@@ -8806,10 +8818,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="C17" t="n">
@@ -8843,10 +8855,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C18" t="n">
@@ -8880,10 +8892,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="C19" t="n">
@@ -8917,10 +8929,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C20" t="n">
@@ -8954,10 +8966,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C21" t="n">
@@ -8991,10 +9003,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C22" t="n">
@@ -9028,10 +9040,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="C23" t="n">
@@ -9065,10 +9077,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C24" t="n">
@@ -9102,10 +9114,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C25" t="n">
@@ -9139,10 +9151,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C26" t="n">
@@ -9176,10 +9188,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="C27" t="n">
@@ -9213,10 +9225,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C28" t="n">
@@ -9250,10 +9262,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C29" t="n">
@@ -9287,10 +9299,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C30" t="n">
@@ -9324,10 +9336,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="C31" t="n">
@@ -9361,10 +9373,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C32" t="n">
@@ -9398,10 +9410,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C33" t="n">
@@ -9435,10 +9447,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C34" t="n">
@@ -9472,10 +9484,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="C35" t="n">
@@ -9509,10 +9521,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C36" t="n">
@@ -9546,10 +9558,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C37" t="n">
@@ -9583,10 +9595,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C38" t="n">
@@ -9620,10 +9632,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="C39" t="n">
@@ -9657,10 +9669,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C40" t="n">
@@ -9694,10 +9706,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C41" t="n">
@@ -9731,10 +9743,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C42" t="n">
@@ -9768,10 +9780,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="C43" t="n">
@@ -9805,10 +9817,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C44" t="n">
@@ -9842,10 +9854,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C45" t="n">
@@ -9879,10 +9891,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C46" t="n">
@@ -9916,10 +9928,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="C47" t="n">
@@ -9953,10 +9965,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C48" t="n">
@@ -9990,10 +10002,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C49" t="n">
@@ -10027,10 +10039,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C50" t="n">
@@ -10064,10 +10076,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="C51" t="n">
@@ -10101,10 +10113,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C52" t="n">
@@ -10138,10 +10150,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C53" t="n">
@@ -10175,10 +10187,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C54" t="n">
@@ -10212,10 +10224,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="C55" t="n">
@@ -10249,10 +10261,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C56" t="n">
@@ -10286,10 +10298,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C57" t="n">
@@ -10323,10 +10335,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C58" t="n">
@@ -10360,10 +10372,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C59" t="n">
@@ -10397,10 +10409,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C60" t="n">
@@ -10434,10 +10446,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C61" t="n">
@@ -10489,12 +10501,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/META.xlsx
+++ b/salidas/empresas/META.xlsx
@@ -498,7 +498,7 @@
         <v>41060</v>
       </c>
       <c r="B2" t="n">
-        <v>29.31919097900391</v>
+        <v>29.31918716430664</v>
       </c>
       <c r="C2" t="n">
         <v>29.60000038146973</v>
@@ -517,7 +517,7 @@
         <v>41090</v>
       </c>
       <c r="B3" t="n">
-        <v>30.80496025085449</v>
+        <v>30.80495643615723</v>
       </c>
       <c r="C3" t="n">
         <v>31.10000038146973</v>
@@ -536,7 +536,7 @@
         <v>41121</v>
       </c>
       <c r="B4" t="n">
-        <v>21.50404167175293</v>
+        <v>21.50403785705566</v>
       </c>
       <c r="C4" t="n">
         <v>21.70999908447266</v>
@@ -561,7 +561,7 @@
         <v>41152</v>
       </c>
       <c r="B5" t="n">
-        <v>17.8886661529541</v>
+        <v>17.888671875</v>
       </c>
       <c r="C5" t="n">
         <v>18.05999946594238</v>
@@ -586,7 +586,7 @@
         <v>41182</v>
       </c>
       <c r="B6" t="n">
-        <v>21.45451354980469</v>
+        <v>21.45451545715332</v>
       </c>
       <c r="C6" t="n">
         <v>21.65999984741211</v>
@@ -611,7 +611,7 @@
         <v>41213</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90973091125488</v>
+        <v>20.90973472595215</v>
       </c>
       <c r="C7" t="n">
         <v>21.11000061035156</v>
@@ -661,7 +661,7 @@
         <v>41274</v>
       </c>
       <c r="B9" t="n">
-        <v>26.36746215820312</v>
+        <v>26.36746025085449</v>
       </c>
       <c r="C9" t="n">
         <v>26.6200008392334</v>
@@ -686,7 +686,7 @@
         <v>41305</v>
       </c>
       <c r="B10" t="n">
-        <v>30.68609619140625</v>
+        <v>30.68610000610352</v>
       </c>
       <c r="C10" t="n">
         <v>30.97999954223633</v>
@@ -711,7 +711,7 @@
         <v>41333</v>
       </c>
       <c r="B11" t="n">
-        <v>26.99148178100586</v>
+        <v>26.99148559570312</v>
       </c>
       <c r="C11" t="n">
         <v>27.25</v>
@@ -736,7 +736,7 @@
         <v>41364</v>
       </c>
       <c r="B12" t="n">
-        <v>25.33732604980469</v>
+        <v>25.33732795715332</v>
       </c>
       <c r="C12" t="n">
         <v>25.57999992370605</v>
@@ -836,7 +836,7 @@
         <v>41486</v>
       </c>
       <c r="B16" t="n">
-        <v>36.45088195800781</v>
+        <v>36.45088577270508</v>
       </c>
       <c r="C16" t="n">
         <v>36.79999923706055</v>
@@ -861,7 +861,7 @@
         <v>41517</v>
       </c>
       <c r="B17" t="n">
-        <v>40.89829254150391</v>
+        <v>40.89828491210938</v>
       </c>
       <c r="C17" t="n">
         <v>41.29000091552734</v>
@@ -886,7 +886,7 @@
         <v>41547</v>
       </c>
       <c r="B18" t="n">
-        <v>49.75348281860352</v>
+        <v>49.75347518920898</v>
       </c>
       <c r="C18" t="n">
         <v>50.22999954223633</v>
@@ -911,7 +911,7 @@
         <v>41578</v>
       </c>
       <c r="B19" t="n">
-        <v>49.73366546630859</v>
+        <v>49.73366165161133</v>
       </c>
       <c r="C19" t="n">
         <v>50.20999908447266</v>
@@ -936,7 +936,7 @@
         <v>41608</v>
       </c>
       <c r="B20" t="n">
-        <v>46.56402587890625</v>
+        <v>46.56402206420898</v>
       </c>
       <c r="C20" t="n">
         <v>47.0099983215332</v>
@@ -986,7 +986,7 @@
         <v>41670</v>
       </c>
       <c r="B22" t="n">
-        <v>61.97640991210938</v>
+        <v>61.97640609741211</v>
       </c>
       <c r="C22" t="n">
         <v>62.56999969482422</v>
@@ -1015,7 +1015,7 @@
         <v>41698</v>
       </c>
       <c r="B23" t="n">
-        <v>67.81053924560547</v>
+        <v>67.81052398681641</v>
       </c>
       <c r="C23" t="n">
         <v>68.45999908447266</v>
@@ -1044,7 +1044,7 @@
         <v>41729</v>
       </c>
       <c r="B24" t="n">
-        <v>59.66851043701172</v>
+        <v>59.66851425170898</v>
       </c>
       <c r="C24" t="n">
         <v>60.2400016784668</v>
@@ -1073,7 +1073,7 @@
         <v>41759</v>
       </c>
       <c r="B25" t="n">
-        <v>59.21287155151367</v>
+        <v>59.21287536621094</v>
       </c>
       <c r="C25" t="n">
         <v>59.77999877929688</v>
@@ -1102,7 +1102,7 @@
         <v>41790</v>
       </c>
       <c r="B26" t="n">
-        <v>62.69948196411133</v>
+        <v>62.69948577880859</v>
       </c>
       <c r="C26" t="n">
         <v>63.29999923706055</v>
@@ -1131,7 +1131,7 @@
         <v>41820</v>
       </c>
       <c r="B27" t="n">
-        <v>66.65162658691406</v>
+        <v>66.65163421630859</v>
       </c>
       <c r="C27" t="n">
         <v>67.29000091552734</v>
@@ -1160,7 +1160,7 @@
         <v>41851</v>
       </c>
       <c r="B28" t="n">
-        <v>71.96077728271484</v>
+        <v>71.96078491210938</v>
       </c>
       <c r="C28" t="n">
         <v>72.65000152587891</v>
@@ -1189,7 +1189,7 @@
         <v>41882</v>
       </c>
       <c r="B29" t="n">
-        <v>74.11020660400391</v>
+        <v>74.11019897460938</v>
       </c>
       <c r="C29" t="n">
         <v>74.81999969482422</v>
@@ -1218,7 +1218,7 @@
         <v>41912</v>
       </c>
       <c r="B30" t="n">
-        <v>78.29016876220703</v>
+        <v>78.29015350341797</v>
       </c>
       <c r="C30" t="n">
         <v>79.04000091552734</v>
@@ -1247,7 +1247,7 @@
         <v>41943</v>
       </c>
       <c r="B31" t="n">
-        <v>74.27858734130859</v>
+        <v>74.27857971191406</v>
       </c>
       <c r="C31" t="n">
         <v>74.98999786376953</v>
@@ -1276,7 +1276,7 @@
         <v>41973</v>
       </c>
       <c r="B32" t="n">
-        <v>76.96288299560547</v>
+        <v>76.96286010742188</v>
       </c>
       <c r="C32" t="n">
         <v>77.69999694824219</v>
@@ -1363,7 +1363,7 @@
         <v>42063</v>
       </c>
       <c r="B35" t="n">
-        <v>78.22081756591797</v>
+        <v>78.2208251953125</v>
       </c>
       <c r="C35" t="n">
         <v>78.97000122070312</v>
@@ -1392,7 +1392,7 @@
         <v>42094</v>
       </c>
       <c r="B36" t="n">
-        <v>81.43999481201172</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="C36" t="n">
         <v>82.22000122070312</v>
@@ -1421,7 +1421,7 @@
         <v>42124</v>
       </c>
       <c r="B37" t="n">
-        <v>78.02272033691406</v>
+        <v>78.02271270751953</v>
       </c>
       <c r="C37" t="n">
         <v>78.76999664306641</v>
@@ -1479,7 +1479,7 @@
         <v>42185</v>
       </c>
       <c r="B39" t="n">
-        <v>84.95632171630859</v>
+        <v>84.95630645751953</v>
       </c>
       <c r="C39" t="n">
         <v>85.76999664306641</v>
@@ -1508,7 +1508,7 @@
         <v>42216</v>
       </c>
       <c r="B40" t="n">
-        <v>93.11815643310547</v>
+        <v>93.11814880371094</v>
       </c>
       <c r="C40" t="n">
         <v>94.01000213623047</v>
@@ -1537,7 +1537,7 @@
         <v>42247</v>
       </c>
       <c r="B41" t="n">
-        <v>88.58159637451172</v>
+        <v>88.58160400390625</v>
       </c>
       <c r="C41" t="n">
         <v>89.43000030517578</v>
@@ -1566,7 +1566,7 @@
         <v>42277</v>
       </c>
       <c r="B42" t="n">
-        <v>89.04713439941406</v>
+        <v>89.04714202880859</v>
       </c>
       <c r="C42" t="n">
         <v>89.90000152587891</v>
@@ -1595,7 +1595,7 @@
         <v>42308</v>
       </c>
       <c r="B43" t="n">
-        <v>101.0026321411133</v>
+        <v>101.0026397705078</v>
       </c>
       <c r="C43" t="n">
         <v>101.9700012207031</v>
@@ -1624,7 +1624,7 @@
         <v>42338</v>
       </c>
       <c r="B44" t="n">
-        <v>103.2510833740234</v>
+        <v>103.2510757446289</v>
       </c>
       <c r="C44" t="n">
         <v>104.2399978637695</v>
@@ -1653,7 +1653,7 @@
         <v>42369</v>
       </c>
       <c r="B45" t="n">
-        <v>103.6671142578125</v>
+        <v>103.6670989990234</v>
       </c>
       <c r="C45" t="n">
         <v>104.6600036621094</v>
@@ -1682,7 +1682,7 @@
         <v>42400</v>
       </c>
       <c r="B46" t="n">
-        <v>111.1454772949219</v>
+        <v>111.1454849243164</v>
       </c>
       <c r="C46" t="n">
         <v>112.2099990844727</v>
@@ -1711,7 +1711,7 @@
         <v>42429</v>
       </c>
       <c r="B47" t="n">
-        <v>105.9056701660156</v>
+        <v>105.9056625366211</v>
       </c>
       <c r="C47" t="n">
         <v>106.9199981689453</v>
@@ -1769,7 +1769,7 @@
         <v>42490</v>
       </c>
       <c r="B49" t="n">
-        <v>116.4645233154297</v>
+        <v>116.4645309448242</v>
       </c>
       <c r="C49" t="n">
         <v>117.5800018310547</v>
@@ -1798,7 +1798,7 @@
         <v>42521</v>
       </c>
       <c r="B50" t="n">
-        <v>117.6828689575195</v>
+        <v>117.6828765869141</v>
       </c>
       <c r="C50" t="n">
         <v>118.8099975585938</v>
@@ -1827,7 +1827,7 @@
         <v>42551</v>
       </c>
       <c r="B51" t="n">
-        <v>113.1958312988281</v>
+        <v>113.1958465576172</v>
       </c>
       <c r="C51" t="n">
         <v>114.2799987792969</v>
@@ -1856,7 +1856,7 @@
         <v>42582</v>
       </c>
       <c r="B52" t="n">
-        <v>122.7642059326172</v>
+        <v>122.7641983032227</v>
       </c>
       <c r="C52" t="n">
         <v>123.9400024414062</v>
@@ -1885,7 +1885,7 @@
         <v>42613</v>
       </c>
       <c r="B53" t="n">
-        <v>124.9235305786133</v>
+        <v>124.9235153198242</v>
       </c>
       <c r="C53" t="n">
         <v>126.120002746582</v>
@@ -1914,7 +1914,7 @@
         <v>42643</v>
       </c>
       <c r="B54" t="n">
-        <v>127.0531387329102</v>
+        <v>127.0531234741211</v>
       </c>
       <c r="C54" t="n">
         <v>128.2700042724609</v>
@@ -1972,7 +1972,7 @@
         <v>42704</v>
       </c>
       <c r="B56" t="n">
-        <v>117.2965621948242</v>
+        <v>117.2965774536133</v>
       </c>
       <c r="C56" t="n">
         <v>118.4199981689453</v>
@@ -2001,7 +2001,7 @@
         <v>42735</v>
       </c>
       <c r="B57" t="n">
-        <v>113.9585418701172</v>
+        <v>113.9585571289062</v>
       </c>
       <c r="C57" t="n">
         <v>115.0500030517578</v>
@@ -2030,7 +2030,7 @@
         <v>42766</v>
       </c>
       <c r="B58" t="n">
-        <v>129.0836791992188</v>
+        <v>129.0836639404297</v>
       </c>
       <c r="C58" t="n">
         <v>130.3200073242188</v>
@@ -2059,7 +2059,7 @@
         <v>42794</v>
       </c>
       <c r="B59" t="n">
-        <v>134.2541351318359</v>
+        <v>134.254150390625</v>
       </c>
       <c r="C59" t="n">
         <v>135.5399932861328</v>
@@ -2088,7 +2088,7 @@
         <v>42825</v>
       </c>
       <c r="B60" t="n">
-        <v>140.7023620605469</v>
+        <v>140.7023773193359</v>
       </c>
       <c r="C60" t="n">
         <v>142.0500030517578</v>
@@ -2117,7 +2117,7 @@
         <v>42855</v>
       </c>
       <c r="B61" t="n">
-        <v>148.8245849609375</v>
+        <v>148.8246002197266</v>
       </c>
       <c r="C61" t="n">
         <v>150.25</v>
@@ -2146,7 +2146,7 @@
         <v>42886</v>
       </c>
       <c r="B62" t="n">
-        <v>150.0231018066406</v>
+        <v>150.0231323242188</v>
       </c>
       <c r="C62" t="n">
         <v>151.4600067138672</v>
@@ -2175,7 +2175,7 @@
         <v>42916</v>
       </c>
       <c r="B63" t="n">
-        <v>149.5476837158203</v>
+        <v>149.5476684570312</v>
       </c>
       <c r="C63" t="n">
         <v>150.9799957275391</v>
@@ -2204,7 +2204,7 @@
         <v>42947</v>
       </c>
       <c r="B64" t="n">
-        <v>167.6443481445312</v>
+        <v>167.6443634033203</v>
       </c>
       <c r="C64" t="n">
         <v>169.25</v>
@@ -2233,7 +2233,7 @@
         <v>42978</v>
       </c>
       <c r="B65" t="n">
-        <v>170.3385467529297</v>
+        <v>170.3385314941406</v>
       </c>
       <c r="C65" t="n">
         <v>171.9700012207031</v>
@@ -2262,7 +2262,7 @@
         <v>43008</v>
       </c>
       <c r="B66" t="n">
-        <v>169.2489776611328</v>
+        <v>169.2489929199219</v>
       </c>
       <c r="C66" t="n">
         <v>170.8699951171875</v>
@@ -2291,7 +2291,7 @@
         <v>43039</v>
       </c>
       <c r="B67" t="n">
-        <v>178.3517761230469</v>
+        <v>178.3518218994141</v>
       </c>
       <c r="C67" t="n">
         <v>180.0599975585938</v>
@@ -2320,7 +2320,7 @@
         <v>43069</v>
       </c>
       <c r="B68" t="n">
-        <v>175.4991455078125</v>
+        <v>175.4991149902344</v>
       </c>
       <c r="C68" t="n">
         <v>177.1799926757812</v>
@@ -2349,7 +2349,7 @@
         <v>43100</v>
       </c>
       <c r="B69" t="n">
-        <v>174.7859649658203</v>
+        <v>174.7859802246094</v>
       </c>
       <c r="C69" t="n">
         <v>176.4600067138672</v>
@@ -2378,7 +2378,7 @@
         <v>43131</v>
       </c>
       <c r="B70" t="n">
-        <v>185.1170196533203</v>
+        <v>185.1169738769531</v>
       </c>
       <c r="C70" t="n">
         <v>186.8899993896484</v>
@@ -2407,7 +2407,7 @@
         <v>43159</v>
       </c>
       <c r="B71" t="n">
-        <v>176.6283111572266</v>
+        <v>176.6283264160156</v>
       </c>
       <c r="C71" t="n">
         <v>178.3200073242188</v>
@@ -2465,7 +2465,7 @@
         <v>43220</v>
       </c>
       <c r="B73" t="n">
-        <v>170.3682556152344</v>
+        <v>170.3682708740234</v>
       </c>
       <c r="C73" t="n">
         <v>172</v>
@@ -2523,7 +2523,7 @@
         <v>43281</v>
       </c>
       <c r="B75" t="n">
-        <v>192.4765319824219</v>
+        <v>192.4765472412109</v>
       </c>
       <c r="C75" t="n">
         <v>194.3200073242188</v>
@@ -2552,7 +2552,7 @@
         <v>43312</v>
       </c>
       <c r="B76" t="n">
-        <v>170.9427795410156</v>
+        <v>170.9427642822266</v>
       </c>
       <c r="C76" t="n">
         <v>172.5800018310547</v>
@@ -2581,7 +2581,7 @@
         <v>43343</v>
       </c>
       <c r="B77" t="n">
-        <v>174.0628662109375</v>
+        <v>174.0628814697266</v>
       </c>
       <c r="C77" t="n">
         <v>175.7299957275391</v>
@@ -2610,7 +2610,7 @@
         <v>43373</v>
       </c>
       <c r="B78" t="n">
-        <v>162.8997955322266</v>
+        <v>162.8998260498047</v>
       </c>
       <c r="C78" t="n">
         <v>164.4600067138672</v>
@@ -2668,7 +2668,7 @@
         <v>43434</v>
       </c>
       <c r="B80" t="n">
-        <v>139.2760620117188</v>
+        <v>139.2760772705078</v>
       </c>
       <c r="C80" t="n">
         <v>140.6100006103516</v>
@@ -2697,7 +2697,7 @@
         <v>43465</v>
       </c>
       <c r="B81" t="n">
-        <v>129.8463745117188</v>
+        <v>129.8463592529297</v>
       </c>
       <c r="C81" t="n">
         <v>131.0899963378906</v>
@@ -2813,7 +2813,7 @@
         <v>43585</v>
       </c>
       <c r="B85" t="n">
-        <v>191.5652313232422</v>
+        <v>191.5652465820312</v>
       </c>
       <c r="C85" t="n">
         <v>193.3999938964844</v>
@@ -2842,7 +2842,7 @@
         <v>43616</v>
       </c>
       <c r="B86" t="n">
-        <v>175.7864074707031</v>
+        <v>175.7863922119141</v>
       </c>
       <c r="C86" t="n">
         <v>177.4700012207031</v>
@@ -2871,7 +2871,7 @@
         <v>43646</v>
       </c>
       <c r="B87" t="n">
-        <v>191.1690368652344</v>
+        <v>191.1690216064453</v>
       </c>
       <c r="C87" t="n">
         <v>193</v>
@@ -2929,7 +2929,7 @@
         <v>43708</v>
       </c>
       <c r="B89" t="n">
-        <v>183.9085998535156</v>
+        <v>183.9085693359375</v>
       </c>
       <c r="C89" t="n">
         <v>185.6699981689453</v>
@@ -2958,7 +2958,7 @@
         <v>43738</v>
       </c>
       <c r="B90" t="n">
-        <v>176.3905792236328</v>
+        <v>176.3905639648438</v>
       </c>
       <c r="C90" t="n">
         <v>178.0800018310547</v>
@@ -2987,7 +2987,7 @@
         <v>43769</v>
       </c>
       <c r="B91" t="n">
-        <v>189.8318634033203</v>
+        <v>189.8318481445312</v>
       </c>
       <c r="C91" t="n">
         <v>191.6499938964844</v>
@@ -3045,7 +3045,7 @@
         <v>43830</v>
       </c>
       <c r="B93" t="n">
-        <v>203.3028411865234</v>
+        <v>203.3028259277344</v>
       </c>
       <c r="C93" t="n">
         <v>205.25</v>
@@ -3074,7 +3074,7 @@
         <v>43861</v>
       </c>
       <c r="B94" t="n">
-        <v>199.9944915771484</v>
+        <v>199.9945220947266</v>
       </c>
       <c r="C94" t="n">
         <v>201.9100036621094</v>
@@ -3103,7 +3103,7 @@
         <v>43890</v>
       </c>
       <c r="B95" t="n">
-        <v>190.6440734863281</v>
+        <v>190.6440887451172</v>
       </c>
       <c r="C95" t="n">
         <v>192.4700012207031</v>
@@ -3132,7 +3132,7 @@
         <v>43921</v>
       </c>
       <c r="B96" t="n">
-        <v>165.2175903320312</v>
+        <v>165.2176208496094</v>
       </c>
       <c r="C96" t="n">
         <v>166.8000030517578</v>
@@ -3161,7 +3161,7 @@
         <v>43951</v>
       </c>
       <c r="B97" t="n">
-        <v>202.7679595947266</v>
+        <v>202.7679443359375</v>
       </c>
       <c r="C97" t="n">
         <v>204.7100067138672</v>
@@ -3190,7 +3190,7 @@
         <v>43982</v>
       </c>
       <c r="B98" t="n">
-        <v>222.9546203613281</v>
+        <v>222.95458984375</v>
       </c>
       <c r="C98" t="n">
         <v>225.0899963378906</v>
@@ -3219,7 +3219,7 @@
         <v>44012</v>
       </c>
       <c r="B99" t="n">
-        <v>224.9158172607422</v>
+        <v>224.9158325195312</v>
       </c>
       <c r="C99" t="n">
         <v>227.0700073242188</v>
@@ -3248,7 +3248,7 @@
         <v>44043</v>
       </c>
       <c r="B100" t="n">
-        <v>251.2634582519531</v>
+        <v>251.2634735107422</v>
       </c>
       <c r="C100" t="n">
         <v>253.6699981689453</v>
@@ -3277,7 +3277,7 @@
         <v>44074</v>
       </c>
       <c r="B101" t="n">
-        <v>290.4185180664062</v>
+        <v>290.4184875488281</v>
       </c>
       <c r="C101" t="n">
         <v>293.2000122070312</v>
@@ -3306,7 +3306,7 @@
         <v>44104</v>
       </c>
       <c r="B102" t="n">
-        <v>259.4154357910156</v>
+        <v>259.4153137207031</v>
       </c>
       <c r="C102" t="n">
         <v>261.8999938964844</v>
@@ -3335,7 +3335,7 @@
         <v>44135</v>
       </c>
       <c r="B103" t="n">
-        <v>260.6139221191406</v>
+        <v>260.6138916015625</v>
       </c>
       <c r="C103" t="n">
         <v>263.1099853515625</v>
@@ -3364,7 +3364,7 @@
         <v>44165</v>
       </c>
       <c r="B104" t="n">
-        <v>274.3423767089844</v>
+        <v>274.3424377441406</v>
       </c>
       <c r="C104" t="n">
         <v>276.9700012207031</v>
@@ -3393,7 +3393,7 @@
         <v>44196</v>
       </c>
       <c r="B105" t="n">
-        <v>270.5685729980469</v>
+        <v>270.568603515625</v>
       </c>
       <c r="C105" t="n">
         <v>273.1600036621094</v>
@@ -3422,7 +3422,7 @@
         <v>44227</v>
       </c>
       <c r="B106" t="n">
-        <v>255.8792572021484</v>
+        <v>255.8792266845703</v>
       </c>
       <c r="C106" t="n">
         <v>258.3299865722656</v>
@@ -3451,7 +3451,7 @@
         <v>44255</v>
       </c>
       <c r="B107" t="n">
-        <v>255.176025390625</v>
+        <v>255.1759948730469</v>
       </c>
       <c r="C107" t="n">
         <v>257.6199951171875</v>
@@ -3480,7 +3480,7 @@
         <v>44286</v>
       </c>
       <c r="B108" t="n">
-        <v>291.73583984375</v>
+        <v>291.7359008789062</v>
       </c>
       <c r="C108" t="n">
         <v>294.5299987792969</v>
@@ -3509,7 +3509,7 @@
         <v>44316</v>
       </c>
       <c r="B109" t="n">
-        <v>321.9960327148438</v>
+        <v>321.9960632324219</v>
       </c>
       <c r="C109" t="n">
         <v>325.0799865722656</v>
@@ -3538,7 +3538,7 @@
         <v>44347</v>
       </c>
       <c r="B110" t="n">
-        <v>325.6114501953125</v>
+        <v>325.6113586425781</v>
       </c>
       <c r="C110" t="n">
         <v>328.7300109863281</v>
@@ -3567,7 +3567,7 @@
         <v>44377</v>
       </c>
       <c r="B111" t="n">
-        <v>344.411376953125</v>
+        <v>344.4112854003906</v>
       </c>
       <c r="C111" t="n">
         <v>347.7099914550781</v>
@@ -3596,7 +3596,7 @@
         <v>44408</v>
       </c>
       <c r="B112" t="n">
-        <v>352.9198303222656</v>
+        <v>352.9198608398438</v>
       </c>
       <c r="C112" t="n">
         <v>356.2999877929688</v>
@@ -3625,7 +3625,7 @@
         <v>44439</v>
       </c>
       <c r="B113" t="n">
-        <v>375.7808837890625</v>
+        <v>375.7809143066406</v>
       </c>
       <c r="C113" t="n">
         <v>379.3800048828125</v>
@@ -3654,7 +3654,7 @@
         <v>44469</v>
       </c>
       <c r="B114" t="n">
-        <v>336.1702880859375</v>
+        <v>336.1702575683594</v>
       </c>
       <c r="C114" t="n">
         <v>339.3900146484375</v>
@@ -3683,7 +3683,7 @@
         <v>44500</v>
       </c>
       <c r="B115" t="n">
-        <v>320.5003051757812</v>
+        <v>320.5003356933594</v>
       </c>
       <c r="C115" t="n">
         <v>323.5700073242188</v>
@@ -3712,7 +3712,7 @@
         <v>44530</v>
       </c>
       <c r="B116" t="n">
-        <v>321.3819274902344</v>
+        <v>321.3818664550781</v>
       </c>
       <c r="C116" t="n">
         <v>324.4599914550781</v>
@@ -3741,7 +3741,7 @@
         <v>44561</v>
       </c>
       <c r="B117" t="n">
-        <v>333.1591491699219</v>
+        <v>333.1590881347656</v>
       </c>
       <c r="C117" t="n">
         <v>336.3500061035156</v>
@@ -3770,7 +3770,7 @@
         <v>44592</v>
       </c>
       <c r="B118" t="n">
-        <v>310.2882385253906</v>
+        <v>310.2881774902344</v>
       </c>
       <c r="C118" t="n">
         <v>313.260009765625</v>
@@ -3886,7 +3886,7 @@
         <v>44712</v>
       </c>
       <c r="B122" t="n">
-        <v>191.8029632568359</v>
+        <v>191.802978515625</v>
       </c>
       <c r="C122" t="n">
         <v>193.6399993896484</v>
@@ -3944,7 +3944,7 @@
         <v>44773</v>
       </c>
       <c r="B124" t="n">
-        <v>157.5906219482422</v>
+        <v>157.5906677246094</v>
       </c>
       <c r="C124" t="n">
         <v>159.1000061035156</v>
@@ -4002,7 +4002,7 @@
         <v>44834</v>
       </c>
       <c r="B126" t="n">
-        <v>134.392822265625</v>
+        <v>134.3928070068359</v>
       </c>
       <c r="C126" t="n">
         <v>135.6799926757812</v>
@@ -4060,7 +4060,7 @@
         <v>44895</v>
       </c>
       <c r="B128" t="n">
-        <v>116.9795989990234</v>
+        <v>116.979606628418</v>
       </c>
       <c r="C128" t="n">
         <v>118.0999984741211</v>
@@ -4089,7 +4089,7 @@
         <v>44926</v>
       </c>
       <c r="B129" t="n">
-        <v>119.198356628418</v>
+        <v>119.1983642578125</v>
       </c>
       <c r="C129" t="n">
         <v>120.3399963378906</v>
@@ -4205,7 +4205,7 @@
         <v>45046</v>
       </c>
       <c r="B133" t="n">
-        <v>238.0401306152344</v>
+        <v>238.0401153564453</v>
       </c>
       <c r="C133" t="n">
         <v>240.3200073242188</v>
@@ -4292,7 +4292,7 @@
         <v>45138</v>
       </c>
       <c r="B136" t="n">
-        <v>315.5774841308594</v>
+        <v>315.5775146484375</v>
       </c>
       <c r="C136" t="n">
         <v>318.6000061035156</v>
@@ -4321,7 +4321,7 @@
         <v>45169</v>
       </c>
       <c r="B137" t="n">
-        <v>293.0829772949219</v>
+        <v>293.0830078125</v>
       </c>
       <c r="C137" t="n">
         <v>295.8900146484375</v>
@@ -4350,7 +4350,7 @@
         <v>45199</v>
       </c>
       <c r="B138" t="n">
-        <v>297.3619689941406</v>
+        <v>297.3619384765625</v>
       </c>
       <c r="C138" t="n">
         <v>300.2099914550781</v>
@@ -4408,7 +4408,7 @@
         <v>45260</v>
       </c>
       <c r="B140" t="n">
-        <v>324.0463562011719</v>
+        <v>324.0463256835938</v>
       </c>
       <c r="C140" t="n">
         <v>327.1499938964844</v>
@@ -4466,7 +4466,7 @@
         <v>45322</v>
       </c>
       <c r="B142" t="n">
-        <v>386.4388122558594</v>
+        <v>386.4388427734375</v>
       </c>
       <c r="C142" t="n">
         <v>390.1400146484375</v>
@@ -4495,7 +4495,7 @@
         <v>45351</v>
       </c>
       <c r="B143" t="n">
-        <v>485.995361328125</v>
+        <v>485.9953308105469</v>
       </c>
       <c r="C143" t="n">
         <v>490.1300048828125</v>
@@ -4524,7 +4524,7 @@
         <v>45382</v>
       </c>
       <c r="B144" t="n">
-        <v>481.4837341308594</v>
+        <v>481.4837036132812</v>
       </c>
       <c r="C144" t="n">
         <v>485.5799865722656</v>
@@ -4553,7 +4553,7 @@
         <v>45412</v>
       </c>
       <c r="B145" t="n">
-        <v>426.5411682128906</v>
+        <v>426.5411376953125</v>
       </c>
       <c r="C145" t="n">
         <v>430.1700134277344</v>
@@ -4582,7 +4582,7 @@
         <v>45443</v>
       </c>
       <c r="B146" t="n">
-        <v>462.891845703125</v>
+        <v>462.8918762207031</v>
       </c>
       <c r="C146" t="n">
         <v>466.8299865722656</v>
@@ -4669,7 +4669,7 @@
         <v>45535</v>
       </c>
       <c r="B149" t="n">
-        <v>517.4256591796875</v>
+        <v>517.425537109375</v>
       </c>
       <c r="C149" t="n">
         <v>521.3099975585938</v>
@@ -4698,7 +4698,7 @@
         <v>45565</v>
       </c>
       <c r="B150" t="n">
-        <v>568.7166137695312</v>
+        <v>568.716552734375</v>
       </c>
       <c r="C150" t="n">
         <v>572.4400024414062</v>
@@ -4727,7 +4727,7 @@
         <v>45596</v>
       </c>
       <c r="B151" t="n">
-        <v>563.8880615234375</v>
+        <v>563.8881225585938</v>
       </c>
       <c r="C151" t="n">
         <v>567.5800170898438</v>
@@ -4872,7 +4872,7 @@
         <v>45747</v>
       </c>
       <c r="B156" t="n">
-        <v>573.5828247070312</v>
+        <v>573.582763671875</v>
       </c>
       <c r="C156" t="n">
         <v>576.3599853515625</v>
@@ -4901,7 +4901,7 @@
         <v>45777</v>
       </c>
       <c r="B157" t="n">
-        <v>546.3545532226562</v>
+        <v>546.3546142578125</v>
       </c>
       <c r="C157" t="n">
         <v>549</v>
@@ -4930,7 +4930,7 @@
         <v>45808</v>
       </c>
       <c r="B158" t="n">
-        <v>644.3700561523438</v>
+        <v>644.3701171875</v>
       </c>
       <c r="C158" t="n">
         <v>647.489990234375</v>
@@ -4988,7 +4988,7 @@
         <v>45869</v>
       </c>
       <c r="B160" t="n">
-        <v>770.3053588867188</v>
+        <v>770.305419921875</v>
       </c>
       <c r="C160" t="n">
         <v>773.4400024414062</v>
@@ -5104,7 +5104,7 @@
         <v>45991</v>
       </c>
       <c r="B164" t="n">
-        <v>645.7595825195312</v>
+        <v>645.759521484375</v>
       </c>
       <c r="C164" t="n">
         <v>647.9500122070312</v>
@@ -5133,7 +5133,7 @@
         <v>46022</v>
       </c>
       <c r="B165" t="n">
-        <v>658.39501953125</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="C165" t="n">
         <v>660.0900268554688</v>
@@ -5162,7 +5162,7 @@
         <v>46053</v>
       </c>
       <c r="B166" t="n">
-        <v>714.6602172851562</v>
+        <v>714.66015625</v>
       </c>
       <c r="C166" t="n">
         <v>716.5</v>
